--- a/outputs/03_abc_slotting.xlsx
+++ b/outputs/03_abc_slotting.xlsx
@@ -22735,7 +22735,7 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -22751,14 +22751,14 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Shelving pick bin</t>
+          <t>Direct from reserve</t>
         </is>
       </c>
       <c r="N322" t="n">
         <v>0</v>
       </c>
       <c r="O322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P322" t="n">
         <v>12.91214953271028</v>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
@@ -22958,14 +22958,14 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Direct from reserve</t>
+          <t>Shelving pick bin</t>
         </is>
       </c>
       <c r="N325" t="n">
         <v>0</v>
       </c>
       <c r="O325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P325" t="n">
         <v>4.305630026809651</v>
